--- a/data/predictions.xlsx
+++ b/data/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,20 +443,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
+          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 1 1 0 0 0
+ 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
+ 1 0 0 1 0 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 0 1 1 0 0 1 1 0 0 0 1 0
+ 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
+ 0 0 1 0 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 1
+ 1 0 0 0 0 1 1 1 0 1 0 1 1 0 0 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 0 1 0 0 0
+ 0 0 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
+ 0 0 0 0 1 0 1 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
+ 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 1 1 0 0 0 0 0 0 0 1 1 0
+ 0 0 0 0 0 1 1 1 0 0 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 0 1 0 0 1 0 1 0 0 1 0 0 1
+ 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
+ 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
+ 0 1 0 0 0 0 1 0 0 0 0 1 1 1 1 0 1 0 1 0 0 0 0 0 0 0 0 1 1 1 1 0 0 0 0 0]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -595,7 +595,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[0 0 0 0 0 0 0 1 1 0 0 1 0 0 0 0 1 0 0 0 0 1 1 0 0 1 0 1 0 0 0 0 0 0 1 0 0
+          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
+ 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
+ 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
+ 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
+ 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
+ 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
+ 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
+ 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
+ 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
+ 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
+ 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
+ 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
+ 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
+ 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
+ 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
+ 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
+ 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
+ 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
+ 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
+ 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
+ 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
+ 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
+ 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
+ 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
+ 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>[0 0 0 0 0 0 0 1 1 0 0 1 0 0 0 0 1 0 0 0 0 1 1 0 0 0 0 1 0 0 0 0 0 0 1 0 0
  0 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 1 0 0 1 1 0 1 0 0 0 0 0 0 0 0 0 0 1 0 0 0
  1 0 0 1 0 1 0 0 0 1 1 0 0 0 0 0 0 0 0 0 1 0 0 0 0 1 0 0 0 0 1 1 0 0 0 1 0
  0 0 0 1 0 1 0 0 0 0 0 1 0 1 0 0 0 0 1 0 0 0 0 0 1 0 1 0 0 1 0 0 0 0 0 0 1
@@ -606,49 +644,11 @@
  0 0 0 0 0 1 0 0 0 0 0 0 0 1 0 1 0 0 0 0 0 1 0 0 0 1 0 0 0 0 0 0 0 0 0 0 1
  0 0 0 1 0 0 1 0 0 0 0 1 0 0 1 0 0 0 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 0 0 0
  0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 1 1 0 0 0 0 1 0 1 0 0 0 1 0 0 0 0 1 0 0 0
- 0 0 0 0 0 0 0 0 0 1 0 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 0 0
+ 0 0 0 0 0 0 0 0 0 1 0 0 0 1 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 0 0
  0 0 1 0 0 0 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 1 0 0 0 1 0 1 0 0
  0 1 0 0 0 0 1 0 0 0 1 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 0 1 0 0 0 0 0 0 0 0]</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 1 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 1 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
-        </is>
-      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
@@ -671,20 +671,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
+          <t>[0 0 0 0 0 0 0 0 1 1 0 1 1 0 0 0 0 0 0 1 0 0 1 0 0 1 0 1 1 0 0 1 0 1 0 0 0
+ 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
+ 0 0 0 1 0 0 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 0 0 0 0 0 0 1 0 0 1 1 0 0 0 1 0
+ 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 0 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 1
+ 0 0 0 0 0 1 1 1 0 1 0 1 1 1 0 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 0 1 0 0 0
+ 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 0 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1 0 0
+ 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 0 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
+ 0 0 0 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 0
+ 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0 0 0 0 0 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 0 1 0 0 1 0 0 0 0 1 0 0 1 0 1 0 0 1 0 0 1
+ 0 1 0 0 0 0 0 1 0 1 1 0 1 0 0 0 1 1 0 1 1 0 0 0 0 1 0 0 1 1 1 0 0 1 0 0 0
+ 1 0 1 1 0 0 1 0 0 0 0 0 1 0 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 1 0
+ 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 0 1 0 0 0 0 0 0 0 0 1 0 0 1 1 0 0 0 0]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -709,12 +709,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 0 0 0 1 0
- 0 0 0 0 0]</t>
+          <t>[0 0 0 0 0 0 0 0 1 1 0 1 1 0 0 0 0 0 0 1 0 0 1 0 0 1 0 1 1 0 0 1 0 1 0 0 0
+ 0 0 0 0 0 1 0 1 0 0 0 0 0 0 0 1 1 0 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
+ 0 0 0 1 0 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 0 0 0 0 0 0 0 0 0 1 0 0 0 0 1 0
+ 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 0 0 0 1 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 1
+ 1 0 0 0 0 1 1 1 0 0 0 0 0 0 0 0 0 1 0 0 0 0 1 0 0 0 0 0 0 0 0 1 0 0 0 0 0
+ 0 0 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0
+ 0 0 0 0 0 0 0 1 0 0 0 1 0 0 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
+ 0 0 0 1 0 1 1 0 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 1 0 0 0 0 0 0 0 0 1 1 0
+ 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0 0 0 0 0 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 1 0 0 0 0 0 1 0 0 0 0 0 0 0 1 0 1 0 0 0 0 0 1 0 1 0 0 0 0 0 0
+ 0 1 0 0 0 0 0 0 0 1 1 0 1 0 0 0 0 0 0 0 1 0 0 0 0 1 0 0 0 1 1 0 0 0 0 0 0
+ 0 0 1 1 0 0 0 0 0 0 1 0 0 0 0 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 1 0
+ 0 1 0 0 0 0 1 0 0 0 0 0 1 1 1 0 1 0 1 0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 0]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -739,12 +747,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 0 0 0 1 0
- 0 0 0 0 0]</t>
+          <t>[0 0 0 0 0 0 0 1 1 0 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 0 0 1 0 0 0
+ 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 0 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
+ 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 0 1 1 0 0 1 1 0 0 0 1 0
+ 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
+ 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 0 1
+ 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 0 1 1 0 0 0
+ 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
+ 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
+ 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
+ 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
+ 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
+ 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
+ 0 1 0 0 0 0 1 0 0 0 0 1 1 1 1 0 1 1 1 0 0 0 0 0 0 0 0 1 1 0 1 0 0 0 0 0]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -769,12 +785,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 0 0 0 1 0
- 0 0 0 0 0]</t>
+          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 0 0 0 1 0 1 1 1 0 1 0 1 0 0 0
+ 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
+ 1 0 0 1 0 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
+ 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
+ 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
+ 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
+ 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
+ 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
+ 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
+ 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
+ 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
+ 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
+ 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -799,12 +823,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 0 0 0 1 0
- 0 0 0 0 0]</t>
+          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
+ 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
+ 1 0 0 1 0 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
+ 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
+ 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
+ 1 0 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
+ 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
+ 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
+ 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
+ 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
+ 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
+ 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 0 0
+ 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -829,9 +861,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 0]</t>
+          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
+ 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
+ 1 0 0 1 0 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
+ 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
+ 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
+ 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
+ 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
+ 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
+ 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
+ 0 0 0 0 0 1 0 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
+ 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
+ 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
+ 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -856,11 +899,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1
- 1 1 1 1 1 1 1 1 0 0 0 0 1 0 0 0]</t>
+          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
+ 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 0 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
+ 1 0 0 0 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
+ 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
+ 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
+ 1 1 0 0 0 1 0 1 0 1 0 1 1 0 0 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
+ 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
+ 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
+ 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 0 1 0 0 0 0 0 0 0 1 1 0
+ 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
+ 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
+ 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
+ 0 1 0 0 0 0 1 0 0 0 0 1 1 0 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -885,20 +937,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 0 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 0 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 0 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 0 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
+          <t>[0 0 0 0 0 0 0 0 1 1 0 1 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 0 0 0 0 0 0
+ 0 0 1 0 0 0 0 0 1 0 0 0 0 0 1 0 1 0 0 1 1 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0
+ 1 1 0 0 0 0 0 1 0 1 1 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 1 0 0 0 0 1 0
+ 0 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 1 0 0 0 0 0 0 0 0 0 1
+ 0 0 1 0 0 1 0 0 0 1 1 0 0 1 0 0 0 0 0 0 1 0 1 0 0 0 0 0 0 0 1 0 0 0 0 1 1
+ 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 0 1 1 1 1 0 0 0 1 0 0 1 0 0 0 0
+ 0 0 1 1 0 0 1 0 0 0 0 0 0 0 1 1 0 0 1 0 1 0 1 0 0 0 0 0 0 1 0 0 0 0 1 0 0
+ 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 0 0 0 1 0 0 0 0 1 0 0
+ 0 0 0 1 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0
+ 0 0 0 1 0 0 1 1 0 0 0 1 0 0 0 0 0 0 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 0 0 0
+ 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 1 0 1 0 0 1 0 1 0 0 0 0 0 1 0 0 0 0 0 0 0 1
+ 0 0 0 0 0 0 0 0 0 1 0 0 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0
+ 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 0 0 1 1 0 1 0 0
+ 0 1 0 0 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 0 0 0 0 0 1 0 1 0 1 0 0 0 0 0 0]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -925,173 +977,21 @@
         <is>
           <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
  0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 0 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 1 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
+ 1 0 0 1 0 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
+ 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
+ 0 0 1 1 0 0 0 0 1 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
+ 1 1 0 0 0 1 1 1 0 1 0 1 1 1 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
+ 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
+ 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
+ 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
+ 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 0 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
+ 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
+ 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 0 1 0 0 1 0 0 0
+ 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
+ 0 1 0 0 0 0 1 0 0 0 0 1 1 1 1 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
-        <is>
-          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 0 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 1 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 0 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 0 1 0 0 1 1 0 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 0 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 0 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 0 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 0 1 0
- 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 0 0 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 0 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>[0 0 0 0 0 0 0 0 1 0 0 1 0 0 0 0 1 0 0 0 0 1 1 0 0 1 0 1 1 0 0 0 0 0 0 0 0
- 0 0 1 0 0 0 0 0 1 0 0 0 0 0 1 0 1 0 0 1 1 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0
- 1 1 0 1 0 0 0 1 0 1 1 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 1 0 0 0 1 0
- 0 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 1 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 1 0 0 0 1 1 0 0 1 0 0 0 0 0 0 1 0 1 0 0 0 0 0 0 0 1 0 0 0 0 1 1
- 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 0
- 0 0 1 0 0 0 1 0 0 0 0 0 0 0 1 1 0 0 1 0 1 0 1 0 0 0 0 0 0 1 0 0 0 0 1 0 0
- 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 0 0 0 1 0 0 0 0 1 0 0
- 0 0 0 1 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0
- 0 0 0 1 0 0 1 1 0 0 0 1 0 0 0 0 0 0 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 0 0 0
- 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 1 0 1 1 0 1 0 1 0 0 0 0 0 1 0 0 0 0 0 0 0 1
- 0 0 0 0 0 0 0 0 0 1 0 0 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 0 0
- 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 0 0 0 0 0 0 1 1 0 1 0 0
- 0 1 0 0 0 0 1 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 1 0 1 0 1 0 0 0 0 0 0]</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 1 1 0 0 0 0 0 0 0 1 1 1 0 0 0
- 0 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 1 0 0 1 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 1 1 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 1 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>[0 0 0 0 0 0 0 0 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
- 0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
- 1 0 0 1 1 1 0 1 0 1 1 0 1 0 0 0 1 0 0 0 1 1 0 0 0 1 1 1 0 0 1 1 0 0 0 1 0
- 0 0 0 0 0 1 0 0 0 1 0 0 0 1 0 1 0 0 1 0 1 0 0 1 0 0 0 0 1 1 0 0 0 0 0 1 1
- 1 0 1 1 0 0 0 0 0 1 1 0 0 1 0 1 0 0 0 1 1 0 1 0 0 1 0 1 0 0 0 0 0 0 0 1 1
- 1 1 0 0 0 1 1 1 0 1 0 1 1 0 1 1 0 1 0 0 0 0 0 1 0 0 0 0 0 0 0 1 0 1 0 0 0
- 0 0 1 0 0 0 0 0 0 0 0 0 0 0 1 1 1 0 0 0 1 0 0 0 0 0 0 1 1 0 0 0 0 0 1 0 0
- 0 0 0 0 1 0 0 1 0 0 0 1 0 1 0 0 1 1 0 1 0 1 1 0 0 0 0 1 0 1 1 0 1 0 1 0 0
- 0 0 1 1 0 1 1 1 0 0 0 0 0 0 0 1 0 0 0 0 0 1 0 0 0 0 1 0 0 0 0 0 0 0 1 1 0
- 0 0 0 0 0 1 1 0 0 1 0 0 0 1 0 0 0 0 0 1 0 0 1 0 0 0 0 0 0 1 0 0 0 0 0 0 1
- 0 0 0 0 0 0 1 0 1 0 0 0 1 1 0 0 1 1 0 0 1 0 1 0 1 1 0 0 1 0 1 0 0 1 0 0 1
- 0 1 0 0 0 0 0 1 1 1 1 0 1 0 0 0 1 1 0 1 1 0 1 0 0 1 0 0 1 1 1 0 0 1 0 0 0
- 1 0 1 1 0 1 1 0 0 0 1 0 1 1 1 0 0 0 0 0 1 1 0 1 1 1 0 0 0 0 0 0 1 1 0 1 0
- 0 1 0 0 0 0 1 0 0 0 0 1 1 1 0 0 1 1 1 0 0 1 0 0 0 0 0 1 1 1 1 1 0 0 0 0]</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
         <is>
           <t>[0 0 0 0 0 0 0 1 1 1 0 1 1 0 0 0 1 1 0 1 0 0 1 0 0 1 0 1 1 1 0 1 0 1 0 0 0
  0 0 0 0 0 1 0 1 0 0 0 1 0 0 0 1 1 0 0 1 1 1 0 0 0 0 0 0 0 0 0 0 0 1 1 0 1
